--- a/exports/trend_1d/FORCEMOT_full_report.xlsx
+++ b/exports/trend_1d/FORCEMOT_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q43"/>
+  <dimension ref="A1:U43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>16.02</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>43760</v>
+        <v>43761</v>
       </c>
       <c r="H2" t="n">
-        <v>1077.65</v>
+        <v>1051.35</v>
       </c>
       <c r="I2" t="n">
         <v>1059.49341404</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K2" t="n">
-        <v>-9.140000000000001</v>
+        <v>-11.36</v>
       </c>
       <c r="L2" t="n">
-        <v>11.05</v>
+        <v>11.64</v>
       </c>
       <c r="M2" t="n">
         <v>1.9</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>43734</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>2</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,28 +626,28 @@
         <v>13.21</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>43770</v>
+        <v>43773</v>
       </c>
       <c r="H3" t="n">
-        <v>1112.55</v>
+        <v>1179.65</v>
       </c>
       <c r="I3" t="n">
         <v>1170.106948956357</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K3" t="n">
-        <v>-5.82</v>
+        <v>-12.2</v>
       </c>
       <c r="L3" t="n">
-        <v>7.77</v>
+        <v>15.09</v>
       </c>
       <c r="M3" t="n">
         <v>1.48</v>
       </c>
       <c r="N3" t="n">
-        <v>2.16</v>
+        <v>6.03</v>
       </c>
       <c r="O3" t="n">
         <v>-2.44</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>13.44</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>43787</v>
+        <v>43788</v>
       </c>
       <c r="H4" t="n">
-        <v>1025.1</v>
+        <v>1022.15</v>
       </c>
       <c r="I4" t="n">
         <v>1022.803286613216</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K4" t="n">
-        <v>-13.1</v>
+        <v>-13.35</v>
       </c>
       <c r="L4" t="n">
         <v>13.85</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,28 +764,28 @@
         <v>13.37</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>43823</v>
+        <v>43825</v>
       </c>
       <c r="H5" t="n">
-        <v>978.9</v>
+        <v>1096.5</v>
       </c>
       <c r="I5" t="n">
         <v>1060.857820070587</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K5" t="n">
-        <v>4.23</v>
+        <v>-7.27</v>
       </c>
       <c r="L5" t="n">
-        <v>4.29</v>
+        <v>10.75</v>
       </c>
       <c r="M5" t="n">
         <v>1.06</v>
       </c>
       <c r="N5" t="n">
-        <v>2.71</v>
+        <v>12.01</v>
       </c>
       <c r="O5" t="n">
         <v>-0.29</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>43797</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>14.48</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>43859</v>
+        <v>43860</v>
       </c>
       <c r="H6" t="n">
-        <v>1313.55</v>
+        <v>1262.6</v>
       </c>
       <c r="I6" t="n">
         <v>1282.594070243996</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>19.79</v>
+        <v>15.15</v>
       </c>
       <c r="L6" t="n">
         <v>11.08</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>43860</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>17.93</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>43937</v>
+        <v>43938</v>
       </c>
       <c r="H7" t="n">
-        <v>802.45</v>
+        <v>888.3</v>
       </c>
       <c r="I7" t="n">
         <v>867.9514034850204</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" t="n">
-        <v>36.44</v>
+        <v>29.65</v>
       </c>
       <c r="L7" t="n">
         <v>11.99</v>
@@ -840,7 +923,7 @@
         <v>8.65</v>
       </c>
       <c r="N7" t="n">
-        <v>9.41</v>
+        <v>10.7</v>
       </c>
       <c r="O7" t="n">
         <v>-3.88</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>43888</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>28.07</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H8" t="n">
-        <v>1053.35</v>
+        <v>1005.7</v>
       </c>
       <c r="I8" t="n">
         <v>1016.022489608987</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="K8" t="n">
-        <v>18.58</v>
+        <v>13.22</v>
       </c>
       <c r="L8" t="n">
         <v>11.63</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>112</v>
+        <v>113</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>18.93</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44152</v>
+        <v>44153</v>
       </c>
       <c r="H9" t="n">
-        <v>1093.2</v>
+        <v>1148.85</v>
       </c>
       <c r="I9" t="n">
         <v>1112.505719344746</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.699999999999999</v>
+        <v>-14.23</v>
       </c>
       <c r="L9" t="n">
-        <v>10.41</v>
+        <v>17.44</v>
       </c>
       <c r="M9" t="n">
         <v>1.81</v>
       </c>
       <c r="N9" t="n">
-        <v>4.45</v>
+        <v>5.09</v>
       </c>
       <c r="O9" t="n">
         <v>-4.52</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>10</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44267</v>
+        <v>44270</v>
       </c>
       <c r="H10" t="n">
-        <v>1296.3</v>
+        <v>1284.7</v>
       </c>
       <c r="I10" t="n">
         <v>1289.302127098948</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="K10" t="n">
-        <v>12.83</v>
+        <v>11.82</v>
       </c>
       <c r="L10" t="n">
         <v>4.64</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>79</v>
+        <v>80</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44161</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5</v>
+      </c>
+      <c r="U10" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>10.4</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44323</v>
+        <v>44326</v>
       </c>
       <c r="H11" t="n">
-        <v>1152.05</v>
+        <v>1203.1</v>
       </c>
       <c r="I11" t="n">
         <v>1192.706934369354</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="K11" t="n">
-        <v>10.33</v>
+        <v>6.35</v>
       </c>
       <c r="L11" t="n">
         <v>2.45</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44280</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>14.44</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44421</v>
+        <v>44424</v>
       </c>
       <c r="H12" t="n">
-        <v>1394.7</v>
+        <v>1367.6</v>
       </c>
       <c r="I12" t="n">
         <v>1383.916266255922</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K12" t="n">
-        <v>15.93</v>
+        <v>13.67</v>
       </c>
       <c r="L12" t="n">
         <v>5.15</v>
@@ -1134,7 +1277,19 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44343</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>16.53</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44452</v>
+        <v>44453</v>
       </c>
       <c r="H13" t="n">
-        <v>1410.95</v>
+        <v>1463.35</v>
       </c>
       <c r="I13" t="n">
         <v>1453.232404281958</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.17</v>
+        <v>-7</v>
       </c>
       <c r="L13" t="n">
-        <v>5.64</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>0.98</v>
       </c>
       <c r="N13" t="n">
-        <v>3.47</v>
+        <v>3.71</v>
       </c>
       <c r="O13" t="n">
         <v>-1.94</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44434</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>11.97</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44518</v>
+        <v>44522</v>
       </c>
       <c r="H14" t="n">
-        <v>1555.3</v>
+        <v>1448.15</v>
       </c>
       <c r="I14" t="n">
         <v>1480.659784116899</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="K14" t="n">
-        <v>6.28</v>
+        <v>-1.04</v>
       </c>
       <c r="L14" t="n">
         <v>4.32</v>
@@ -1239,7 +1406,7 @@
         <v>1.42</v>
       </c>
       <c r="N14" t="n">
-        <v>5.21</v>
+        <v>6.89</v>
       </c>
       <c r="O14" t="n">
         <v>3.71</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44469</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>20.28</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44652</v>
+        <v>44655</v>
       </c>
       <c r="H15" t="n">
-        <v>1091.05</v>
+        <v>1132.8</v>
       </c>
       <c r="I15" t="n">
         <v>1122.575856631986</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K15" t="n">
-        <v>24.66</v>
+        <v>21.78</v>
       </c>
       <c r="L15" t="n">
         <v>8.06</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>92</v>
+        <v>93</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>6</v>
+      </c>
+      <c r="U15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>12.85</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44691</v>
+        <v>44692</v>
       </c>
       <c r="H16" t="n">
-        <v>1047.4</v>
+        <v>1014.15</v>
       </c>
       <c r="I16" t="n">
         <v>1045.198781136292</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K16" t="n">
-        <v>-7.54</v>
+        <v>-10.47</v>
       </c>
       <c r="L16" t="n">
-        <v>8.94</v>
+        <v>11.72</v>
       </c>
       <c r="M16" t="n">
         <v>3.58</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>19.71</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44739</v>
+        <v>44740</v>
       </c>
       <c r="H17" t="n">
-        <v>936.45</v>
+        <v>1061.05</v>
       </c>
       <c r="I17" t="n">
         <v>1043.279889646074</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K17" t="n">
-        <v>7.66</v>
+        <v>-4.62</v>
       </c>
       <c r="L17" t="n">
         <v>10.53</v>
@@ -1410,7 +1613,7 @@
         <v>1.88</v>
       </c>
       <c r="N17" t="n">
-        <v>3.09</v>
+        <v>13.31</v>
       </c>
       <c r="O17" t="n">
         <v>-3.17</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>17.63</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44827</v>
+        <v>44830</v>
       </c>
       <c r="H18" t="n">
-        <v>1311.35</v>
+        <v>1224.1</v>
       </c>
       <c r="I18" t="n">
         <v>1249.89726751236</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="K18" t="n">
-        <v>23.59</v>
+        <v>15.37</v>
       </c>
       <c r="L18" t="n">
         <v>11.55</v>
@@ -1467,7 +1682,7 @@
         <v>3.22</v>
       </c>
       <c r="N18" t="n">
-        <v>3.5</v>
+        <v>6.65</v>
       </c>
       <c r="O18" t="n">
         <v>13.31</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>4</v>
+      </c>
+      <c r="U18" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>17.13</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H19" t="n">
-        <v>1366.65</v>
+        <v>1458.4</v>
       </c>
       <c r="I19" t="n">
         <v>1392.132513815831</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K19" t="n">
-        <v>-11.65</v>
+        <v>-19.14</v>
       </c>
       <c r="L19" t="n">
-        <v>14.99</v>
+        <v>20.73</v>
       </c>
       <c r="M19" t="n">
-        <v>1.91</v>
+        <v>5.37</v>
       </c>
       <c r="N19" t="n">
-        <v>5.23</v>
+        <v>6.71</v>
       </c>
       <c r="O19" t="n">
         <v>-6.65</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,22 +1799,22 @@
         <v>12.57</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44916</v>
+        <v>44917</v>
       </c>
       <c r="H20" t="n">
-        <v>1425.2</v>
+        <v>1398.75</v>
       </c>
       <c r="I20" t="n">
         <v>1406.667623240227</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.28</v>
+        <v>-4.09</v>
       </c>
       <c r="L20" t="n">
-        <v>3.62</v>
+        <v>6.05</v>
       </c>
       <c r="M20" t="n">
         <v>1.09</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>12.94</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>44932</v>
+        <v>44935</v>
       </c>
       <c r="H21" t="n">
-        <v>1502.55</v>
+        <v>1544.1</v>
       </c>
       <c r="I21" t="n">
         <v>1531.515007716104</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.42</v>
+        <v>-10.39</v>
       </c>
       <c r="L21" t="n">
         <v>13.32</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,28 +1937,28 @@
         <v>12.24</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>44966</v>
+        <v>44967</v>
       </c>
       <c r="H22" t="n">
-        <v>1441.3</v>
+        <v>1343.6</v>
       </c>
       <c r="I22" t="n">
         <v>1409.077398760234</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K22" t="n">
-        <v>-6.66</v>
+        <v>-12.98</v>
       </c>
       <c r="L22" t="n">
-        <v>10.24</v>
+        <v>13.54</v>
       </c>
       <c r="M22" t="n">
         <v>1.03</v>
       </c>
       <c r="N22" t="n">
-        <v>2.48</v>
+        <v>6.78</v>
       </c>
       <c r="O22" t="n">
         <v>2.77</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>14.83</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45016</v>
+        <v>45019</v>
       </c>
       <c r="H23" t="n">
-        <v>1165.35</v>
+        <v>1233.8</v>
       </c>
       <c r="I23" t="n">
         <v>1233.510870093456</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K23" t="n">
-        <v>13.27</v>
+        <v>8.17</v>
       </c>
       <c r="L23" t="n">
         <v>7.17</v>
@@ -1752,7 +2027,7 @@
         <v>1.14</v>
       </c>
       <c r="N23" t="n">
-        <v>4.28</v>
+        <v>5.87</v>
       </c>
       <c r="O23" t="n">
         <v>-6.78</v>
@@ -1761,7 +2036,19 @@
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>3</v>
+      </c>
+      <c r="U23" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>13.48</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45219</v>
+        <v>45222</v>
       </c>
       <c r="H24" t="n">
-        <v>3714.45</v>
+        <v>3528.75</v>
       </c>
       <c r="I24" t="n">
         <v>3623.307115112993</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="K24" t="n">
-        <v>201.06</v>
+        <v>186.01</v>
       </c>
       <c r="L24" t="n">
         <v>5.5</v>
@@ -1809,7 +2096,7 @@
         <v>1.26</v>
       </c>
       <c r="N24" t="n">
-        <v>4.84</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>5.87</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>137</v>
+        <v>138</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>7</v>
+      </c>
+      <c r="U24" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>13.7</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45224</v>
+        <v>45336</v>
       </c>
       <c r="H25" t="n">
-        <v>3352.35</v>
+        <v>4422.65</v>
       </c>
       <c r="I25" t="n">
         <v>3882.04527913026</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>2</v>
+        <v>114</v>
       </c>
       <c r="K25" t="n">
-        <v>5</v>
+        <v>-25.33</v>
       </c>
       <c r="L25" t="n">
-        <v>4.85</v>
+        <v>29.99</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>31.25</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>31.93</v>
       </c>
       <c r="O25" t="n">
         <v>-5</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45224</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>17.06</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45433</v>
+        <v>45434</v>
       </c>
       <c r="H26" t="n">
-        <v>8698.049999999999</v>
+        <v>8509.450000000001</v>
       </c>
       <c r="I26" t="n">
         <v>8523.863514430839</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K26" t="n">
-        <v>96.67</v>
+        <v>92.41</v>
       </c>
       <c r="L26" t="n">
         <v>3.9</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>16.37</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45464</v>
+        <v>45467</v>
       </c>
       <c r="H27" t="n">
-        <v>8887.65</v>
+        <v>9344.5</v>
       </c>
       <c r="I27" t="n">
         <v>9306.411509487229</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>-4.44</v>
+        <v>-9.81</v>
       </c>
       <c r="L27" t="n">
-        <v>9.880000000000001</v>
+        <v>10.88</v>
       </c>
       <c r="M27" t="n">
         <v>3.61</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>14.77</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45509</v>
+        <v>45510</v>
       </c>
       <c r="H28" t="n">
-        <v>8522.75</v>
+        <v>8262.4</v>
       </c>
       <c r="I28" t="n">
         <v>8324.172525243548</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K28" t="n">
-        <v>-8.789999999999999</v>
+        <v>-11.58</v>
       </c>
       <c r="L28" t="n">
         <v>14.28</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>3</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>15.44</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45561</v>
+        <v>45562</v>
       </c>
       <c r="H29" t="n">
-        <v>6961.45</v>
+        <v>7629</v>
       </c>
       <c r="I29" t="n">
         <v>7622.575116225603</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K29" t="n">
-        <v>15.75</v>
+        <v>7.67</v>
       </c>
       <c r="L29" t="n">
         <v>10.44</v>
@@ -2094,7 +2441,7 @@
         <v>1.66</v>
       </c>
       <c r="N29" t="n">
-        <v>7.3</v>
+        <v>9.59</v>
       </c>
       <c r="O29" t="n">
         <v>-3.05</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,22 +2489,22 @@
         <v>15.58</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45586</v>
+        <v>45587</v>
       </c>
       <c r="H30" t="n">
-        <v>6760.3</v>
+        <v>6508.15</v>
       </c>
       <c r="I30" t="n">
         <v>6650.007667676189</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K30" t="n">
-        <v>-11.39</v>
+        <v>-14.69</v>
       </c>
       <c r="L30" t="n">
-        <v>11.65</v>
+        <v>14.8</v>
       </c>
       <c r="M30" t="n">
         <v>0.64</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>15.35</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45594</v>
+        <v>45595</v>
       </c>
       <c r="H31" t="n">
-        <v>6384.95</v>
+        <v>7661.9</v>
       </c>
       <c r="I31" t="n">
         <v>7143.404679406173</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K31" t="n">
-        <v>1.89</v>
+        <v>-17.73</v>
       </c>
       <c r="L31" t="n">
-        <v>4.65</v>
+        <v>17.73</v>
       </c>
       <c r="M31" t="n">
-        <v>1.16</v>
+        <v>13.14</v>
       </c>
       <c r="N31" t="n">
-        <v>3.31</v>
+        <v>20</v>
       </c>
       <c r="O31" t="n">
         <v>-3.73</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S31" t="b">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>18.95</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
       <c r="H32" t="n">
-        <v>6944.9</v>
+        <v>6704.05</v>
       </c>
       <c r="I32" t="n">
         <v>6813.960802357449</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K32" t="n">
-        <v>-9.359999999999999</v>
+        <v>-12.5</v>
       </c>
       <c r="L32" t="n">
-        <v>9.94</v>
+        <v>12.82</v>
       </c>
       <c r="M32" t="n">
         <v>0.34</v>
@@ -2274,7 +2657,19 @@
         <v>1</v>
       </c>
       <c r="Q32" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>16.35</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45658</v>
+        <v>45659</v>
       </c>
       <c r="H33" t="n">
-        <v>6629.45</v>
+        <v>7256.85</v>
       </c>
       <c r="I33" t="n">
         <v>7008.813322660458</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K33" t="n">
-        <v>1.11</v>
+        <v>-8.25</v>
       </c>
       <c r="L33" t="n">
-        <v>6.64</v>
+        <v>12.32</v>
       </c>
       <c r="M33" t="n">
         <v>1.98</v>
       </c>
       <c r="N33" t="n">
-        <v>3.99</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O33" t="n">
         <v>-3.47</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>12.74</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45665</v>
+        <v>45666</v>
       </c>
       <c r="H34" t="n">
-        <v>6853.25</v>
+        <v>6544.2</v>
       </c>
       <c r="I34" t="n">
         <v>6547.584512780527</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.56</v>
+        <v>-9.82</v>
       </c>
       <c r="L34" t="n">
-        <v>8.75</v>
+        <v>10.08</v>
       </c>
       <c r="M34" t="n">
         <v>0.8100000000000001</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>15.82</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45719</v>
+        <v>45720</v>
       </c>
       <c r="H35" t="n">
-        <v>6944.3</v>
+        <v>7154.05</v>
       </c>
       <c r="I35" t="n">
         <v>7000.662929616909</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K35" t="n">
-        <v>-6.11</v>
+        <v>-9.32</v>
       </c>
       <c r="L35" t="n">
-        <v>8.19</v>
+        <v>11.06</v>
       </c>
       <c r="M35" t="n">
         <v>1.06</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>13.98</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45903</v>
+        <v>45904</v>
       </c>
       <c r="H36" t="n">
-        <v>19785</v>
+        <v>18086</v>
       </c>
       <c r="I36" t="n">
         <v>18476.87447226158</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="K36" t="n">
-        <v>176.56</v>
+        <v>152.81</v>
       </c>
       <c r="L36" t="n">
         <v>4.24</v>
@@ -2493,7 +2924,7 @@
         <v>9.31</v>
       </c>
       <c r="N36" t="n">
-        <v>8.34</v>
+        <v>8.59</v>
       </c>
       <c r="O36" t="n">
         <v>3.02</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>124</v>
+        <v>125</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>7</v>
+      </c>
+      <c r="U36" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>22.58</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="H37" t="n">
-        <v>17098</v>
+        <v>17654</v>
       </c>
       <c r="I37" t="n">
         <v>17584.40668710021</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K37" t="n">
-        <v>5.46</v>
+        <v>2.39</v>
       </c>
       <c r="L37" t="n">
         <v>11.91</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>3</v>
+      </c>
+      <c r="U37" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>12.32</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="H38" t="n">
-        <v>20020</v>
+        <v>18710</v>
       </c>
       <c r="I38" t="n">
         <v>18925.76504505612</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K38" t="n">
-        <v>13.4</v>
+        <v>5.98</v>
       </c>
       <c r="L38" t="n">
         <v>7</v>
@@ -2607,7 +3062,7 @@
         <v>0.43</v>
       </c>
       <c r="N38" t="n">
-        <v>3.47</v>
+        <v>6.54</v>
       </c>
       <c r="O38" t="n">
         <v>3.25</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>3</v>
+      </c>
+      <c r="U38" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="39">
@@ -2643,22 +3110,22 @@
         <v>15.94</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="H39" t="n">
-        <v>21390</v>
+        <v>22361</v>
       </c>
       <c r="I39" t="n">
         <v>21691.65205393868</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K39" t="n">
-        <v>-14.32</v>
+        <v>-19.51</v>
       </c>
       <c r="L39" t="n">
-        <v>18.65</v>
+        <v>19.99</v>
       </c>
       <c r="M39" t="n">
         <v>3.61</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>15.38</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="H40" t="n">
-        <v>23380</v>
+        <v>21450</v>
       </c>
       <c r="I40" t="n">
         <v>22261.49148938541</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K40" t="n">
-        <v>4.56</v>
+        <v>-4.07</v>
       </c>
       <c r="L40" t="n">
-        <v>3.73</v>
+        <v>5.19</v>
       </c>
       <c r="M40" t="n">
         <v>5.1</v>
       </c>
       <c r="N40" t="n">
-        <v>4.38</v>
+        <v>8.25</v>
       </c>
       <c r="O40" t="n">
         <v>4.54</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>20.6</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="H41" t="n">
-        <v>18330</v>
+        <v>19269</v>
       </c>
       <c r="I41" t="n">
         <v>18849.64950029128</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K41" t="n">
-        <v>14.55</v>
+        <v>10.17</v>
       </c>
       <c r="L41" t="n">
         <v>9.51</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>6</v>
+      </c>
+      <c r="U41" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="42">
@@ -2814,22 +3317,22 @@
         <v>11.04</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46290</v>
+        <v>46293</v>
       </c>
       <c r="H42" t="n">
-        <v>17388</v>
+        <v>17100</v>
       </c>
       <c r="I42" t="n">
         <v>17141.86104815944</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K42" t="n">
-        <v>-9.76</v>
+        <v>-11.26</v>
       </c>
       <c r="L42" t="n">
-        <v>11.34</v>
+        <v>11.56</v>
       </c>
       <c r="M42" t="n">
         <v>0.96</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2895,6 +3410,14 @@
       <c r="Q43" t="n">
         <v>21</v>
       </c>
+      <c r="R43" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5881,7 +6404,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>58.5</v>
+        <v>63</v>
       </c>
     </row>
     <row r="6">
@@ -5891,7 +6414,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7">
@@ -5901,7 +6424,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>203</v>
       </c>
     </row>
     <row r="8">
@@ -5911,7 +6434,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9">
@@ -5921,7 +6444,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69</v>
+        <v>78</v>
       </c>
     </row>
     <row r="10">
@@ -5931,7 +6454,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
     </row>
     <row r="11">
@@ -5941,7 +6464,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12">
@@ -5951,7 +6474,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13">
@@ -5961,7 +6484,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29.3</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14">
@@ -5971,7 +6494,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14.25</v>
+        <v>7.58</v>
       </c>
     </row>
     <row r="15">
@@ -5981,7 +6504,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24.08</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="16">
@@ -5991,7 +6514,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.94</v>
+        <v>-3.93</v>
       </c>
     </row>
     <row r="17">
@@ -6001,7 +6524,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>201.06</v>
+        <v>186.01</v>
       </c>
     </row>
     <row r="18">
@@ -6011,7 +6534,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>56.1</v>
+        <v>39</v>
       </c>
     </row>
     <row r="19">
@@ -6021,7 +6544,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>8.73</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="20">
@@ -6031,7 +6554,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>8.94</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="21">
@@ -6041,7 +6564,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>18.65</v>
+        <v>29.99</v>
       </c>
     </row>
     <row r="22">
@@ -6051,7 +6574,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -6061,7 +6584,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -6071,7 +6594,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.35</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="25">
@@ -6081,7 +6604,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>9.31</v>
+        <v>31.25</v>
       </c>
     </row>
     <row r="26">
@@ -6091,7 +6614,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>5.25</v>
+        <v>7.72</v>
       </c>
     </row>
     <row r="27">
@@ -6101,7 +6624,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.82</v>
+        <v>31.93</v>
       </c>
     </row>
     <row r="28">
@@ -6111,7 +6634,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29">
